--- a/Data/educacion.xlsx
+++ b/Data/educacion.xlsx
@@ -1,21 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATOS\Desktop\UT_2026A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\documentos\UNIVERSIDAD\CUARTO SEMESTRE\Estadistica 1\ULTIMO INTENTO\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD6C8AED-26F2-456E-AB1A-A7F40901DDA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53A67909-7FC1-4EF2-B9F9-C61BF5ED92F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dataset_educacion_matematica" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -82,13 +87,13 @@
     <t>Promedio</t>
   </si>
   <si>
-    <t>Asistencia (%)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tecnologia </t>
   </si>
   <si>
     <t>Satisfaccion</t>
+  </si>
+  <si>
+    <t>Asistencia</t>
   </si>
 </sst>
 </file>
@@ -479,13 +484,13 @@
         <v>19</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
